--- a/data/trans_bre/P45C_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R2-Provincia-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 8,16</t>
+          <t>-4,55; 8,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 1,63</t>
+          <t>-11,15; 1,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 1,27</t>
+          <t>-11,48; 1,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 79,72</t>
+          <t>-29,0; 91,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 11,41</t>
+          <t>-51,43; 8,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 9,47</t>
+          <t>-48,74; 8,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 1,19</t>
+          <t>-9,59; 1,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 1,98</t>
+          <t>-6,02; 2,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 6,51</t>
+          <t>-2,16; 6,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 3,71</t>
+          <t>-7,59; 3,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 5,78</t>
+          <t>-34,86; 5,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,15; 18,65</t>
+          <t>-42,71; 22,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 62,44</t>
+          <t>-15,58; 58,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 27,24</t>
+          <t>-34,93; 24,99</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 4,12</t>
+          <t>-6,4; 3,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,62; -7,52</t>
+          <t>-19,83; -6,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 7,94</t>
+          <t>-1,64; 7,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,3</t>
+          <t>-2,55; 5,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 42,78</t>
+          <t>-41,53; 35,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,36; -27,99</t>
+          <t>-59,77; -23,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 118,92</t>
+          <t>-15,99; 116,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 117,88</t>
+          <t>-32,67; 122,1</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,71; -4,29</t>
+          <t>-15,91; -5,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 0,25</t>
+          <t>-8,89; 0,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 2,6</t>
+          <t>-7,07; 2,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 0,41</t>
+          <t>-15,68; -0,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,09; -21,91</t>
+          <t>-60,51; -24,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,02; 4,93</t>
+          <t>-59,29; 5,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,64; 24,1</t>
+          <t>-42,49; 25,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,7; 3,61</t>
+          <t>-71,12; -2,45</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 5,04</t>
+          <t>-3,56; 5,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 6,18</t>
+          <t>-6,46; 5,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -0,91</t>
+          <t>-6,2; -0,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 2,36</t>
+          <t>-5,15; 2,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 155,11</t>
+          <t>-46,74; 144,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 77,97</t>
+          <t>-45,36; 69,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-69,07; 71,66</t>
+          <t>-68,51; 90,07</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -2,14</t>
+          <t>-15,8; -1,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,18; -2,03</t>
+          <t>-18,16; -2,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 4,82</t>
+          <t>-0,94; 4,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 13,55</t>
+          <t>0,9; 14,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,82; -9,49</t>
+          <t>-53,98; -7,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,78; -6,62</t>
+          <t>-49,04; -10,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 506,86</t>
+          <t>-32,94; 552,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 75,69</t>
+          <t>3,29; 76,93</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 0,5</t>
+          <t>-6,66; 0,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 0,4</t>
+          <t>-9,02; 0,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 5,66</t>
+          <t>-2,7; 5,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 1,35</t>
+          <t>-10,51; 1,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 4,5</t>
+          <t>-45,57; 2,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,4; 2,42</t>
+          <t>-31,61; 1,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 45,99</t>
+          <t>-16,06; 46,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 10,23</t>
+          <t>-65,63; 15,25</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 1,84</t>
+          <t>-4,25; 1,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,23</t>
+          <t>-2,92; 2,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 3,1</t>
+          <t>-4,36; 3,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 8,05</t>
+          <t>-15,34; 7,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,39; 22,08</t>
+          <t>-36,0; 21,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 36,04</t>
+          <t>-32,59; 40,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 17,96</t>
+          <t>-20,23; 20,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 63,46</t>
+          <t>-46,98; 59,6</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,54</t>
+          <t>-5,02; -1,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -2,46</t>
+          <t>-5,87; -2,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,78</t>
+          <t>-1,78; 1,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,41</t>
+          <t>-5,7; 0,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-30,3; -10,23</t>
+          <t>-30,18; -11,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -14,79</t>
+          <t>-31,51; -14,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 13,7</t>
+          <t>-12,48; 12,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 1,39</t>
+          <t>-34,65; 2,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P45C_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 8,47</t>
+          <t>-3,35; 7,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 1,1</t>
+          <t>-11,22; 1,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 1,5</t>
+          <t>-11,36; 0,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 91,71</t>
+          <t>-23,58; 85,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,43; 8,45</t>
+          <t>-52,67; 10,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,74; 8,95</t>
+          <t>-49,03; 5,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-9,93%</t>
+          <t>-9,4%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 1,08</t>
+          <t>-9,29; 1,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 2,09</t>
+          <t>-6,2; 1,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 6,37</t>
+          <t>-2,36; 6,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 3,55</t>
+          <t>-7,25; 3,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 5,49</t>
+          <t>-34,33; 7,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,71; 22,28</t>
+          <t>-42,81; 16,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 58,4</t>
+          <t>-15,7; 58,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 24,99</t>
+          <t>-34,86; 25,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 3,71</t>
+          <t>-6,55; 3,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,83; -6,39</t>
+          <t>-19,86; -6,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 7,92</t>
+          <t>-1,77; 8,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 5,47</t>
+          <t>-3,17; 4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,53; 35,09</t>
+          <t>-41,34; 39,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,77; -23,5</t>
+          <t>-59,56; -24,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 116,28</t>
+          <t>-15,6; 122,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 122,1</t>
+          <t>-36,71; 89,83</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,77</t>
+          <t>-3,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-39,19%</t>
+          <t>-24,62%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,91; -5,05</t>
+          <t>-15,79; -4,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 0,59</t>
+          <t>-8,98; 0,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 2,85</t>
+          <t>-7,55; 2,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,68; -0,41</t>
+          <t>-10,37; 2,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,51; -24,87</t>
+          <t>-60,38; -23,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,29; 5,57</t>
+          <t>-60,32; 3,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,49; 25,42</t>
+          <t>-45,76; 23,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,12; -2,45</t>
+          <t>-52,44; 20,82</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>-2,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-24,86%</t>
+          <t>-37,76%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 5,12</t>
+          <t>-3,98; 5,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 5,57</t>
+          <t>-6,12; 6,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,2; -0,94</t>
+          <t>-7,02; -1,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 2,83</t>
+          <t>-5,92; 1,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,74; 144,83</t>
+          <t>-49,36; 157,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 69,6</t>
+          <t>-42,58; 77,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 49,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 90,07</t>
+          <t>-71,08; 59,75</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>7,81</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,8; -1,86</t>
+          <t>-16,39; -2,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,16; -2,93</t>
+          <t>-18,48; -3,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,94</t>
+          <t>-1,03; 4,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 14,22</t>
+          <t>1,47; 14,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,98; -7,66</t>
+          <t>-55,98; -11,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,04; -10,27</t>
+          <t>-49,0; -9,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 552,02</t>
+          <t>-35,75; 440,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 76,93</t>
+          <t>5,64; 79,94</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-26,1%</t>
+          <t>-6,43%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 0,29</t>
+          <t>-7,15; 0,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 0,42</t>
+          <t>-8,64; 0,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 5,52</t>
+          <t>-2,47; 6,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 1,99</t>
+          <t>-5,04; 3,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 2,91</t>
+          <t>-46,51; 3,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 1,86</t>
+          <t>-30,45; 4,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 46,64</t>
+          <t>-14,74; 49,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-65,63; 15,25</t>
+          <t>-30,89; 24,89</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-5,65</t>
+          <t>-14,31</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-23,69%</t>
+          <t>-44,44%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 1,93</t>
+          <t>-4,18; 2,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,45</t>
+          <t>-2,93; 2,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 3,5</t>
+          <t>-4,52; 3,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 7,07</t>
+          <t>-18,57; -9,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 21,52</t>
+          <t>-35,3; 22,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 40,72</t>
+          <t>-33,1; 40,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 20,53</t>
+          <t>-21,07; 19,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 59,6</t>
+          <t>-52,99; -33,51</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,1</t>
+          <t>-3,64</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-20,11%</t>
+          <t>-21,43%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,66</t>
+          <t>-5,0; -1,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -2,35</t>
+          <t>-5,68; -2,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,59</t>
+          <t>-1,63; 1,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,54</t>
+          <t>-5,42; -1,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-30,18; -11,33</t>
+          <t>-30,11; -11,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,51; -14,13</t>
+          <t>-30,73; -14,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 12,44</t>
+          <t>-11,5; 13,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 2,31</t>
+          <t>-29,8; -11,9</t>
         </is>
       </c>
     </row>
